--- a/Result/profitability/2441.xlsx
+++ b/Result/profitability/2441.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.78</v>
       </c>
       <c r="M2" t="n">
-        <v>1.085</v>
+        <v>1.13375</v>
       </c>
       <c r="N2" t="n">
-        <v>21.5175</v>
+        <v>21.6275</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.03</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06625</v>
+        <v>1.135</v>
       </c>
       <c r="N3" t="n">
-        <v>21.99</v>
+        <v>22.5525</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.11</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0775</v>
+        <v>1.14375</v>
       </c>
       <c r="N4" t="n">
-        <v>23.155</v>
+        <v>23.59125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>0.98875</v>
+        <v>1.08125</v>
       </c>
       <c r="N5" t="n">
-        <v>22.6425</v>
+        <v>22.94</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.15</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9037500000000001</v>
+        <v>0.93625</v>
       </c>
       <c r="N6" t="n">
-        <v>21.2125</v>
+        <v>21.96125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8274999999999999</v>
+        <v>0.88375</v>
       </c>
       <c r="N7" t="n">
-        <v>21.90875</v>
+        <v>22.45125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.91</v>
       </c>
       <c r="M8" t="n">
-        <v>0.80125</v>
+        <v>0.8225</v>
       </c>
       <c r="N8" t="n">
-        <v>22.535</v>
+        <v>22.6125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.9</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7675</v>
+        <v>0.7675000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>21.9775</v>
@@ -1772,7 +1772,7 @@
         <v>0.99</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7625</v>
+        <v>0.7625000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>21.51625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2441</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5284</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4003</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1281</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1083</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>20.50%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>27</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1110</v>
+      </c>
+      <c r="K75" t="n">
+        <v>895</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.18375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>21.475</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1700000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1214285714285714</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.620000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.02623783326280149</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.7400000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.8915662650602412</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.379999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1088248742569731</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
